--- a/forms/trg/Formulir_TRG_ctrg.xlsx
+++ b/forms/trg/Formulir_TRG_ctrg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B28)</f>
+        <f>COUNTA(Anggota!B5:B29)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F28)</f>
+        <f>COUNTA(Anggota!F5:F29)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,22 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. H. Adi Suryadi Culla MA</t>
+          <t>Prof. Seniwati, Ph.D</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Democracy and Global Civil Society</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Counter Terrorism</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,7 +937,7 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-6316-522X</t>
+          <t>0000-0002-0483-9116</t>
         </is>
       </c>
       <c r="K5" s="12" t="n"/>
@@ -954,17 +954,17 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ariana, S.IP., M.Si.</t>
+          <t>Dr. H. Adi Suryadi Culla MA</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>Democracy and Global Civil Society</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -978,7 +978,7 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0009-0001-6080-2043</t>
+          <t>0000-0002-6316-522X</t>
         </is>
       </c>
       <c r="K6" s="12" t="n"/>
@@ -995,17 +995,17 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Rahmatia, MA</t>
+          <t>Dr. Ariana, S.IP., M.Si.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Economy</t>
+          <t>Politics</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0009-0009-7550-9243</t>
+          <t>0009-0001-6080-2043</t>
         </is>
       </c>
       <c r="K7" s="12" t="n"/>
@@ -1036,29 +1036,33 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Chumphon Angkananon</t>
+          <t>Prof. Dr. Rahmatia, MA</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Security and Peace Studies</t>
+          <t>Economy</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Maejo University, Thailand</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>0009-0009-7550-9243</t>
+        </is>
+      </c>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="12" t="n"/>
       <c r="M8" s="11" t="inlineStr">
@@ -1073,33 +1077,29 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>David Jimoh Kayode</t>
+          <t>Chumphon Angkananon</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Research Methodology</t>
+          <t>Security and Peace Studies</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>University of Ilorin, Nigeria</t>
+          <t>Maejo University, Thailand</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-9200-249X</t>
-        </is>
-      </c>
+      <c r="J9" s="12" t="n"/>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="12" t="n"/>
       <c r="M9" s="11" t="inlineStr">
@@ -1114,22 +1114,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Munif Arif Ranti, S.IP., MA</t>
+          <t>David Jimoh Kayode</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Human Security</t>
+          <t>Research Methodology</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>University of Ilorin, Nigeria</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1138,7 +1138,7 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-2415-3007</t>
+          <t>0000-0001-9200-249X</t>
         </is>
       </c>
       <c r="K10" s="12" t="n"/>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Rhin Khairina Rahmat, S.IP., M.A</t>
+          <t>Munif Arif Ranti, S.IP., MA</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Sustainable Development</t>
+          <t>Human Security</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -1179,7 +1179,7 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0009-0001-3109-8544</t>
+          <t>0000-0002-2415-3007</t>
         </is>
       </c>
       <c r="K11" s="12" t="n"/>
@@ -1196,17 +1196,17 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Fajhriyadi Hastira, S.IP., M.H.I</t>
+          <t>Rhin Khairina Rahmat, S.IP., M.A</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Human Right</t>
+          <t>Sustainable Development</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -1220,7 +1220,7 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-0900-0782</t>
+          <t>0009-0001-3109-8544</t>
         </is>
       </c>
       <c r="K12" s="12" t="n"/>
@@ -1237,25 +1237,33 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Nurul Ilmi</t>
+          <t>Muhammad Fajhriyadi Hastira, S.IP., M.H.I</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
+          <t>Human Right</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E13" s="11" t="n"/>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
-      <c r="J13" s="12" t="n"/>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-0900-0782</t>
+        </is>
+      </c>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="12" t="n"/>
       <c r="M13" s="11" t="inlineStr">
@@ -1270,24 +1278,20 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Ainun Djaria</t>
+          <t>Nurul Ilmi</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>International Relations</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
           <t>Hasanuddin University</t>
         </is>
       </c>
+      <c r="E14" s="11" t="n"/>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
@@ -1307,12 +1311,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Aisyiah Putri Haris</t>
+          <t>Ainun Djaria</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1344,17 +1348,17 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Alfania Laela Azzahra</t>
+          <t>Aisyiah Putri Haris</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Politics</t>
+          <t>International Relations</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -1379,10 +1383,26 @@
       <c r="A17" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="11" t="n"/>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Alfania Laela Azzahra</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Counter Terrorism Research Group (CTRG) under the Thematic Research Group (TRG) of Hasanuddin University provides an important academic platform for advancing interdisciplinary research on terrorism, security, and tourism.</t>
+        </is>
+      </c>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
@@ -1390,7 +1410,11 @@
       <c r="J17" s="12" t="n"/>
       <c r="K17" s="12" t="n"/>
       <c r="L17" s="12" t="n"/>
-      <c r="M17" s="12" t="n"/>
+      <c r="M17" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1579,15 +1603,32 @@
       <c r="L28" s="12" t="n"/>
       <c r="M28" s="12" t="n"/>
     </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="12" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="12" t="n"/>
+      <c r="M29" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
